--- a/example/reports/reporting_firewall-review.xlsx
+++ b/example/reports/reporting_firewall-review.xlsx
@@ -70,7 +70,7 @@
     <t>Backup timestamp</t>
   </si>
   <si>
-    <t>2026-07-30 18:33</t>
+    <t>2026-07-30 19:26</t>
   </si>
   <si>
     <t>Report generated</t>

--- a/example/reports/reporting_firewall-review.xlsx
+++ b/example/reports/reporting_firewall-review.xlsx
@@ -70,7 +70,7 @@
     <t>Backup timestamp</t>
   </si>
   <si>
-    <t>2026-07-30 19:26</t>
+    <t>2026-08-04 22:41</t>
   </si>
   <si>
     <t>Report generated</t>
@@ -448,7 +448,7 @@
     <t>Expires soon</t>
   </si>
   <si>
-    <t>The stated expiry is 2026-08-27, in 28 days.</t>
+    <t>The stated expiry is 2026-08-27, in 23 days.</t>
   </si>
   <si>
     <t>Confirm whether the access is still needed before it lapses.</t>

--- a/example/reports/reporting_firewall-review.xlsx
+++ b/example/reports/reporting_firewall-review.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="160">
   <si>
     <t>Firewall Rule Review</t>
   </si>
@@ -70,12 +70,15 @@
     <t>Backup timestamp</t>
   </si>
   <si>
-    <t>2026-08-04 22:41</t>
+    <t>2026-08-05 00:22</t>
   </si>
   <si>
     <t>Report generated</t>
   </si>
   <si>
+    <t>2026-08-05 00:23</t>
+  </si>
+  <si>
     <t>Tool version</t>
   </si>
   <si>
@@ -175,18 +178,18 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Peer (other side)</t>
+  </si>
+  <si>
+    <t>Peer addresses</t>
+  </si>
+  <si>
     <t>Your networks</t>
   </si>
   <si>
     <t>Your networks (addresses)</t>
   </si>
   <si>
-    <t>Peer (other side)</t>
-  </si>
-  <si>
-    <t>Peer addresses</t>
-  </si>
-  <si>
     <t>Peer team</t>
   </si>
   <si>
@@ -448,7 +451,7 @@
     <t>Expires soon</t>
   </si>
   <si>
-    <t>The stated expiry is 2026-08-27, in 23 days.</t>
+    <t>The stated expiry is 2026-08-27, in 22 days.</t>
   </si>
   <si>
     <t>Confirm whether the access is still needed before it lapses.</t>
@@ -1012,20 +1015,20 @@
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="4">
         <v>2</v>
@@ -1033,7 +1036,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="4">
         <v>0</v>
@@ -1041,7 +1044,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="4">
         <v>0</v>
@@ -1049,7 +1052,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="4">
         <v>2</v>
@@ -1057,7 +1060,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="4">
         <v>0</v>
@@ -1065,7 +1068,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="4">
         <v>14</v>
@@ -1073,7 +1076,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="4">
         <v>2</v>
@@ -1081,20 +1084,20 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="B24" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1102,27 +1105,27 @@
     </row>
     <row r="26" spans="1:2">
       <c r="B26" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="B27" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="B28" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="B29" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="B30" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1130,7 +1133,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="B32" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1138,7 +1141,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="B34" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1146,7 +1149,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="B36" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1154,22 +1157,22 @@
     </row>
     <row r="38" spans="1:2">
       <c r="B38" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="B39" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="B42" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1190,8 +1193,8 @@
     <col min="6" max="6" width="34.7109375" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="10" width="30.7109375" customWidth="1"/>
-    <col min="11" max="12" width="38.7109375" customWidth="1"/>
+    <col min="9" max="10" width="38.7109375" customWidth="1"/>
+    <col min="11" max="12" width="30.7109375" customWidth="1"/>
     <col min="13" max="13" width="16.7109375" customWidth="1"/>
     <col min="14" max="15" width="26.7109375" customWidth="1"/>
     <col min="16" max="16" width="24.7109375" customWidth="1"/>
@@ -1206,76 +1209,76 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1312,76 +1315,76 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="M1" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1418,208 +1421,208 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="M1" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="8">
         <v>6</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="L2" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X2" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3" s="8">
         <v>17</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="L3" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
       <c r="V3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W3" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1665,336 +1668,336 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="M1" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="8">
         <v>3</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U2" s="8"/>
       <c r="V2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W2" s="8"/>
       <c r="X2" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3" s="8">
         <v>8</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U3" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W3" s="8"/>
       <c r="X3" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" s="8">
         <v>14</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W4" s="8"/>
       <c r="X4" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" s="8">
         <v>19</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2038,696 +2041,696 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="M1" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D2" s="8">
         <v>4</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J2" s="8"/>
       <c r="K2" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U2" s="8"/>
       <c r="V2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W2" s="8"/>
       <c r="X2" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D3" s="8">
         <v>15</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U3" s="8"/>
       <c r="V3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W3" s="8"/>
       <c r="X3" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" s="8">
         <v>4</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W4" s="8"/>
       <c r="X4" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" s="8">
         <v>15</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U5" s="8"/>
       <c r="V5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D6" s="8">
         <v>4</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U6" s="8"/>
       <c r="V6" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W6" s="8"/>
       <c r="X6" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D7" s="8">
         <v>15</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>121</v>
-      </c>
       <c r="H7" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W7" s="8"/>
       <c r="X7" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D8" s="8">
         <v>4</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U8" s="8"/>
       <c r="V8" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W8" s="8"/>
       <c r="X8" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D9" s="8">
         <v>15</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F9" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>125</v>
-      </c>
       <c r="H9" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S9" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U9" s="8"/>
       <c r="V9" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W9" s="8"/>
       <c r="X9" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D10" s="8">
         <v>4</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M10" s="8"/>
       <c r="N10" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U10" s="8"/>
       <c r="V10" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W10" s="8"/>
       <c r="X10" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D11" s="8">
         <v>15</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F11" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>129</v>
-      </c>
       <c r="H11" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U11" s="8"/>
       <c r="V11" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W11" s="8"/>
       <c r="X11" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2764,71 +2767,71 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2849,24 +2852,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C2" s="8">
         <v>0</v>
@@ -2895,39 +2898,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F2" s="8"/>
     </row>

--- a/example/reports/reporting_firewall-review.xlsx
+++ b/example/reports/reporting_firewall-review.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="159">
   <si>
     <t>Firewall Rule Review</t>
   </si>
@@ -70,15 +70,12 @@
     <t>Backup timestamp</t>
   </si>
   <si>
-    <t>2026-08-05 00:22</t>
+    <t>2026-08-07 16:09</t>
   </si>
   <si>
     <t>Report generated</t>
   </si>
   <si>
-    <t>2026-08-05 00:23</t>
-  </si>
-  <si>
     <t>Tool version</t>
   </si>
   <si>
@@ -451,7 +448,7 @@
     <t>Expires soon</t>
   </si>
   <si>
-    <t>The stated expiry is 2026-08-27, in 22 days.</t>
+    <t>The stated expiry is 2026-08-27, in 20 days.</t>
   </si>
   <si>
     <t>Confirm whether the access is still needed before it lapses.</t>
@@ -1015,20 +1012,20 @@
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4">
         <v>2</v>
@@ -1036,7 +1033,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4">
         <v>0</v>
@@ -1044,7 +1041,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4">
         <v>0</v>
@@ -1052,7 +1049,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" s="4">
         <v>2</v>
@@ -1060,7 +1057,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" s="4">
         <v>0</v>
@@ -1068,7 +1065,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" s="4">
         <v>14</v>
@@ -1076,7 +1073,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="4">
         <v>2</v>
@@ -1084,20 +1081,20 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="B24" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1105,27 +1102,27 @@
     </row>
     <row r="26" spans="1:2">
       <c r="B26" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="B27" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="B28" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="B29" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="B30" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1133,7 +1130,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="B32" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1141,7 +1138,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="B34" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1149,7 +1146,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="B36" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1157,22 +1154,22 @@
     </row>
     <row r="38" spans="1:2">
       <c r="B38" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="B39" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="B42" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1209,76 +1206,76 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1315,76 +1312,76 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1421,208 +1418,208 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="8">
         <v>6</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>75</v>
-      </c>
       <c r="Q2" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="R2" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="S2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="T2" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="U2" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="V2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="W2" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="V2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="W2" s="10" t="s">
+      <c r="X2" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" s="8">
         <v>17</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="P3" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="P3" s="8" t="s">
-        <v>75</v>
-      </c>
       <c r="Q3" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="S3" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>77</v>
       </c>
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
       <c r="V3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W3" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="X3" s="8" t="s">
         <v>85</v>
-      </c>
-      <c r="X3" s="8" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1668,336 +1665,336 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="8">
         <v>3</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>88</v>
-      </c>
       <c r="G2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I2" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P2" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="R2" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="S2" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="R2" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="S2" s="8" t="s">
+      <c r="T2" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="T2" s="9" t="s">
-        <v>92</v>
       </c>
       <c r="U2" s="8"/>
       <c r="V2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W2" s="8"/>
       <c r="X2" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" s="8">
         <v>8</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F3" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>95</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>96</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P3" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q3" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="R3" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="T3" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="R3" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="T3" s="9" t="s">
+      <c r="U3" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="U3" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="V3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W3" s="8"/>
       <c r="X3" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" s="8">
         <v>14</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I4" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O4" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="R4" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="P4" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="R4" s="8" t="s">
+      <c r="S4" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="S4" s="8" t="s">
-        <v>78</v>
-      </c>
       <c r="T4" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W4" s="8"/>
       <c r="X4" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" s="8">
         <v>19</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I5" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K5" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>95</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>96</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q5" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="Q5" s="8" t="s">
-        <v>98</v>
-      </c>
       <c r="R5" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2041,696 +2038,696 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D2" s="8">
         <v>4</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>112</v>
       </c>
       <c r="J2" s="8"/>
       <c r="K2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U2" s="8"/>
       <c r="V2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W2" s="8"/>
       <c r="X2" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="8">
         <v>15</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>112</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U3" s="8"/>
       <c r="V3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W3" s="8"/>
       <c r="X3" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" s="8">
         <v>4</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I4" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W4" s="8"/>
       <c r="X4" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" s="8">
         <v>15</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I5" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U5" s="8"/>
       <c r="V5" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D6" s="8">
         <v>4</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F6" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>122</v>
-      </c>
       <c r="H6" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U6" s="8"/>
       <c r="V6" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W6" s="8"/>
       <c r="X6" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D7" s="8">
         <v>15</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W7" s="8"/>
       <c r="X7" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D8" s="8">
         <v>4</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F8" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>126</v>
-      </c>
       <c r="H8" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U8" s="8"/>
       <c r="V8" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W8" s="8"/>
       <c r="X8" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D9" s="8">
         <v>15</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S9" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U9" s="8"/>
       <c r="V9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W9" s="8"/>
       <c r="X9" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D10" s="8">
         <v>4</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F10" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>130</v>
-      </c>
       <c r="H10" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M10" s="8"/>
       <c r="N10" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U10" s="8"/>
       <c r="V10" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W10" s="8"/>
       <c r="X10" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D11" s="8">
         <v>15</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U11" s="8"/>
       <c r="V11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W11" s="8"/>
       <c r="X11" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2767,71 +2764,71 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>140</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>144</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2852,24 +2849,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C2" s="8">
         <v>0</v>
@@ -2898,39 +2895,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>158</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>159</v>
       </c>
       <c r="F2" s="8"/>
     </row>

--- a/example/reports/reporting_firewall-review.xlsx
+++ b/example/reports/reporting_firewall-review.xlsx
@@ -70,7 +70,7 @@
     <t>Backup timestamp</t>
   </si>
   <si>
-    <t>2026-08-07 16:09</t>
+    <t>2026-08-26 23:14</t>
   </si>
   <si>
     <t>Report generated</t>
@@ -448,7 +448,7 @@
     <t>Expires soon</t>
   </si>
   <si>
-    <t>The stated expiry is 2026-08-27, in 20 days.</t>
+    <t>The stated expiry is 2026-08-27, in 1 days.</t>
   </si>
   <si>
     <t>Confirm whether the access is still needed before it lapses.</t>
